--- a/plantWork-tracker.xlsx
+++ b/plantWork-tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10329"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nbicloud-my.sharepoint.com/personal/wez23nor_nbi_ac_uk/Documents/Experiment/plantWork-tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1901" documentId="8_{D8DCFB22-01BC-924B-AE1D-F4EDC42DDFA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54AD51F2-F219-8F41-8959-035F644BF845}"/>
+  <xr:revisionPtr revIDLastSave="1921" documentId="8_{D8DCFB22-01BC-924B-AE1D-F4EDC42DDFA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED8179FE-C512-404F-B394-4D6222D8BAC7}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{76529944-D650-424B-8087-6FB9D5F1FA19}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{76529944-D650-424B-8087-6FB9D5F1FA19}"/>
   </bookViews>
   <sheets>
     <sheet name="Inventory" sheetId="10" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="71">
   <si>
     <t>Notes</t>
   </si>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>Empty entry</t>
+  </si>
+  <si>
+    <t>Transformation_End</t>
   </si>
 </sst>
 </file>
@@ -257,9 +260,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="172" formatCode="d/m/yy;@"/>
+    <numFmt numFmtId="164" formatCode="d/m/yy;@"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -309,12 +312,6 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFFC000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -502,11 +499,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -528,26 +525,26 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="172" fontId="4" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="4" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -565,33 +562,33 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="4" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -631,10 +628,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -697,6 +690,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -707,6 +710,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -757,6 +780,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -767,6 +810,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -777,6 +830,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -787,6 +860,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -797,6 +880,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -817,6 +920,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -827,36 +940,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -866,96 +949,6 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.14996795556505021"/>
@@ -978,12 +971,12 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="9" tint="0.39994506668294322"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="5" tint="0.39994506668294322"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="0.39994506668294322"/>
       </font>
     </dxf>
     <dxf>
@@ -1041,6 +1034,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1353,17 +1350,20 @@
     <col min="8" max="8" width="8.5" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.33203125" style="4" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="8.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5" style="3" customWidth="1"/>
     <col min="13" max="13" width="10.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.5" style="3" customWidth="1"/>
-    <col min="15" max="16" width="8.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.33203125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="9.1640625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="8.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10.33203125" style="4" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="8.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.1640625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="8.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.33203125" style="4" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="9.5" style="3" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="8.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.1640625" style="2" customWidth="1"/>
     <col min="25" max="25" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="9.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="8.33203125" style="37" bestFit="1" customWidth="1"/>
@@ -1379,73 +1379,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="D1" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="47" t="s">
+      <c r="E1" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="47" t="s">
+      <c r="F1" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="54" t="s">
+      <c r="G1" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="53" t="s">
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="57" t="s">
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
-      <c r="S1" s="55" t="s">
+      <c r="P1" s="55"/>
+      <c r="Q1" s="55"/>
+      <c r="R1" s="55"/>
+      <c r="S1" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="T1" s="55"/>
-      <c r="U1" s="55"/>
-      <c r="V1" s="55"/>
-      <c r="W1" s="56" t="s">
+      <c r="T1" s="53"/>
+      <c r="U1" s="53"/>
+      <c r="V1" s="53"/>
+      <c r="W1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="X1" s="56"/>
-      <c r="Y1" s="56"/>
-      <c r="Z1" s="56"/>
-      <c r="AA1" s="58" t="s">
+      <c r="X1" s="54"/>
+      <c r="Y1" s="54"/>
+      <c r="Z1" s="54"/>
+      <c r="AA1" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="AB1" s="58"/>
-      <c r="AC1" s="58" t="s">
+      <c r="AB1" s="56"/>
+      <c r="AC1" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="AD1" s="51" t="s">
+      <c r="AD1" s="49" t="s">
         <v>0</v>
       </c>
       <c r="AE1" s="15"/>
     </row>
     <row r="2" spans="1:31" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
+      <c r="A2" s="44"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
       <c r="G2" s="24" t="s">
         <v>23</v>
       </c>
@@ -1506,21 +1506,21 @@
       <c r="Z2" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="AA2" s="41" t="s">
+      <c r="AA2" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="AB2" s="41" t="s">
+      <c r="AB2" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="AC2" s="59"/>
-      <c r="AD2" s="52"/>
+      <c r="AC2" s="57"/>
+      <c r="AD2" s="50"/>
       <c r="AE2" s="16"/>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" s="37">
-        <v>45728</v>
-      </c>
-      <c r="B3" s="61" t="s">
+        <v>45898</v>
+      </c>
+      <c r="B3" s="42" t="s">
         <v>63</v>
       </c>
       <c r="C3" s="37" t="s">
@@ -1529,84 +1529,84 @@
       <c r="D3" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="E3" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="39">
+      <c r="F3" s="38">
         <f ca="1">Action!$B$3-A3</f>
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G3" s="37">
         <f>$A3+Action!$B$4</f>
-        <v>45753</v>
+        <v>45923</v>
       </c>
       <c r="H3" s="37">
         <f>$A3+Action!$B$5</f>
-        <v>45763</v>
+        <v>45933</v>
       </c>
       <c r="I3" s="4">
         <f ca="1">$F3-Action!$B$4</f>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>61</v>
       </c>
       <c r="K3" s="37">
         <f>$A3+Action!$B$6</f>
-        <v>45768</v>
+        <v>45938</v>
       </c>
       <c r="L3" s="37">
-        <f>$A3+Action!$B$8</f>
-        <v>45778</v>
-      </c>
-      <c r="M3" s="39">
+        <f>$A3+Action!$B$7</f>
+        <v>45948</v>
+      </c>
+      <c r="M3" s="38">
         <f ca="1">$F3-Action!$B$6</f>
-        <v>-7</v>
+        <v>-14</v>
       </c>
       <c r="N3" s="37" t="s">
         <v>15</v>
       </c>
       <c r="O3" s="37">
+        <f>$A3+Action!$B$10</f>
+        <v>45958</v>
+      </c>
+      <c r="P3" s="37">
         <f>$A3+Action!$B$11</f>
-        <v>45788</v>
-      </c>
-      <c r="P3" s="37">
-        <f>$A3+Action!$B$12</f>
-        <v>45798</v>
-      </c>
-      <c r="Q3" s="39">
-        <f ca="1">$F3-Action!$B$9</f>
-        <v>-12</v>
+        <v>45968</v>
+      </c>
+      <c r="Q3" s="38">
+        <f ca="1">$F3-Action!$B$8</f>
+        <v>-19</v>
       </c>
       <c r="R3" s="37" t="s">
         <v>15</v>
       </c>
       <c r="S3" s="37">
+        <f>$A3+Action!$B$10</f>
+        <v>45958</v>
+      </c>
+      <c r="T3" s="37">
         <f>$A3+Action!$B$11</f>
-        <v>45788</v>
-      </c>
-      <c r="T3" s="37">
-        <f>$A3+Action!$B$12</f>
-        <v>45798</v>
-      </c>
-      <c r="U3" s="39">
-        <f ca="1">$F3-Action!$B$11</f>
-        <v>-27</v>
+        <v>45968</v>
+      </c>
+      <c r="U3" s="38">
+        <f ca="1">$F3-Action!$B$10</f>
+        <v>-34</v>
       </c>
       <c r="V3" s="37" t="s">
         <v>15</v>
       </c>
       <c r="W3" s="37">
+        <f>$A3+Action!$B$12</f>
+        <v>45973</v>
+      </c>
+      <c r="X3" s="37">
         <f>$A3+Action!$B$13</f>
-        <v>45803</v>
-      </c>
-      <c r="X3" s="37">
-        <f>$A3+Action!$B$14</f>
-        <v>45823</v>
-      </c>
-      <c r="Y3" s="39">
-        <f ca="1">$F3-Action!$B$13</f>
-        <v>-42</v>
+        <v>45993</v>
+      </c>
+      <c r="Y3" s="38">
+        <f ca="1">$F3-Action!$B$12</f>
+        <v>-49</v>
       </c>
       <c r="Z3" s="37" t="s">
         <v>15</v>
@@ -1619,11 +1619,11 @@
         <f t="shared" ref="AB3" si="1">AA3+10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AC3" s="40"/>
+      <c r="AC3" s="39"/>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
-        <v>45700</v>
+        <v>45800</v>
       </c>
       <c r="B4" s="30" t="s">
         <v>65</v>
@@ -1639,15 +1639,15 @@
       </c>
       <c r="F4" s="4">
         <f ca="1">Action!$B$3-A4</f>
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="G4" s="3">
         <f>$A4+Action!$B$4</f>
-        <v>45725</v>
+        <v>45825</v>
       </c>
       <c r="H4" s="3">
         <f>$A4+Action!$B$5</f>
-        <v>45735</v>
+        <v>45835</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>34</v>
@@ -1668,12 +1668,12 @@
         <v>37</v>
       </c>
       <c r="O4" s="3">
+        <f>$A4+Action!$B$10</f>
+        <v>45860</v>
+      </c>
+      <c r="P4" s="3">
         <f>$A4+Action!$B$11</f>
-        <v>45760</v>
-      </c>
-      <c r="P4" s="3">
-        <f>$A4+Action!$B$12</f>
-        <v>45770</v>
+        <v>45870</v>
       </c>
       <c r="Q4" s="4" t="s">
         <v>34</v>
@@ -1682,31 +1682,31 @@
         <v>45396</v>
       </c>
       <c r="S4" s="3">
+        <f>$A4+Action!$B$10</f>
+        <v>45860</v>
+      </c>
+      <c r="T4" s="3">
         <f>$A4+Action!$B$11</f>
-        <v>45760</v>
-      </c>
-      <c r="T4" s="3">
-        <f>$A4+Action!$B$12</f>
-        <v>45770</v>
+        <v>45870</v>
       </c>
       <c r="U4" s="4">
-        <f ca="1">$F4-Action!$B$11</f>
-        <v>1</v>
+        <f ca="1">$F4-Action!$B$10</f>
+        <v>64</v>
       </c>
       <c r="V4" s="3" t="s">
         <v>15</v>
       </c>
       <c r="W4" s="3">
+        <f>$A4+Action!$B$12</f>
+        <v>45875</v>
+      </c>
+      <c r="X4" s="3">
         <f>$A4+Action!$B$13</f>
-        <v>45775</v>
-      </c>
-      <c r="X4" s="3">
-        <f>$A4+Action!$B$14</f>
-        <v>45795</v>
+        <v>45895</v>
       </c>
       <c r="Y4" s="4">
-        <f ca="1">$F4-Action!$B$13</f>
-        <v>-14</v>
+        <f ca="1">$F4-Action!$B$12</f>
+        <v>49</v>
       </c>
       <c r="Z4" s="3" t="s">
         <v>15</v>
@@ -1725,7 +1725,7 @@
       <c r="A5" s="3">
         <v>45673</v>
       </c>
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="42" t="s">
         <v>66</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="F5" s="4">
         <f ca="1">Action!$B$3-A5</f>
-        <v>88</v>
+        <v>251</v>
       </c>
       <c r="G5" s="3">
         <f>$A5+Action!$B$4</f>
@@ -1768,11 +1768,11 @@
         <v>37</v>
       </c>
       <c r="O5" s="3">
+        <f>$A5+Action!$B$10</f>
+        <v>45733</v>
+      </c>
+      <c r="P5" s="3">
         <f>$A5+Action!$B$11</f>
-        <v>45733</v>
-      </c>
-      <c r="P5" s="3">
-        <f>$A5+Action!$B$12</f>
         <v>45743</v>
       </c>
       <c r="Q5" s="4" t="s">
@@ -1782,11 +1782,11 @@
         <v>45715</v>
       </c>
       <c r="S5" s="3">
+        <f>$A5+Action!$B$10</f>
+        <v>45733</v>
+      </c>
+      <c r="T5" s="3">
         <f>$A5+Action!$B$11</f>
-        <v>45733</v>
-      </c>
-      <c r="T5" s="3">
-        <f>$A5+Action!$B$12</f>
         <v>45743</v>
       </c>
       <c r="U5" s="4" t="s">
@@ -1796,11 +1796,11 @@
         <v>15</v>
       </c>
       <c r="W5" s="3">
+        <f>$A5+Action!$B$12</f>
+        <v>45748</v>
+      </c>
+      <c r="X5" s="3">
         <f>$A5+Action!$B$13</f>
-        <v>45748</v>
-      </c>
-      <c r="X5" s="3">
-        <f>$A5+Action!$B$14</f>
         <v>45768</v>
       </c>
       <c r="Y5" s="4" t="s">
@@ -1817,16 +1817,18 @@
         <f t="shared" ref="AB5" si="3">AA5+10</f>
         <v>45750</v>
       </c>
-      <c r="AC5" s="37"/>
+      <c r="AC5" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="AB6" s="40"/>
+      <c r="AB6" s="39"/>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="61"/>
+      <c r="B7" s="42"/>
       <c r="C7" s="3" t="s">
         <v>36</v>
       </c>
@@ -1860,7 +1862,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="L7" s="3" t="e">
-        <f>$A7+Action!$B$8</f>
+        <f>$A7+Action!$B$7</f>
         <v>#VALUE!</v>
       </c>
       <c r="M7" s="4" t="e">
@@ -1871,56 +1873,56 @@
         <v>15</v>
       </c>
       <c r="O7" s="3" t="e">
+        <f>$A7+Action!$B$10</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="P7" s="3" t="e">
         <f>$A7+Action!$B$11</f>
         <v>#VALUE!</v>
       </c>
-      <c r="P7" s="3" t="e">
+      <c r="Q7" s="4" t="e">
+        <f ca="1">$F7-Action!$B$10</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="S7" s="3" t="e">
+        <f>$A7+Action!$B$10</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="T7" s="3" t="e">
+        <f>$A7+Action!$B$11</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U7" s="4" t="e">
+        <f ca="1">$F7-Action!$B$10</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="V7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="W7" s="3" t="e">
         <f>$A7+Action!$B$12</f>
         <v>#VALUE!</v>
       </c>
-      <c r="Q7" s="4" t="e">
-        <f ca="1">$F7-Action!$B$11</f>
+      <c r="X7" s="3" t="e">
+        <f>$A7+Action!$B$13</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R7" s="3" t="s">
+      <c r="Y7" s="4" t="e">
+        <f ca="1">$F7-Action!$B$12</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="S7" s="3" t="e">
-        <f>$A7+Action!$B$11</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="T7" s="3" t="e">
+      <c r="AA7" s="37" t="e">
         <f>$A7+Action!$B$12</f>
         <v>#VALUE!</v>
       </c>
-      <c r="U7" s="4" t="e">
-        <f ca="1">$F7-Action!$B$11</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="V7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="W7" s="3" t="e">
+      <c r="AB7" s="37" t="e">
         <f>$A7+Action!$B$13</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X7" s="3" t="e">
-        <f>$A7+Action!$B$14</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Y7" s="4" t="e">
-        <f ca="1">$F7-Action!$B$13</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Z7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA7" s="37" t="e">
-        <f>$A7+Action!$B$13</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AB7" s="37" t="e">
-        <f>$A7+Action!$B$14</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -1948,15 +1950,17 @@
       <formula>NOT(ISERROR(SEARCH("to",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:AE1 A2:AB2 AD2:AE2 AP1:XFD2 AD4:XFD4 A3:AC5 A6:XFD1048576">
+  <conditionalFormatting sqref="A3:AC5 A1:AE1 AP1:XFD2 A2:AB2 AD2:AE2 AD4:XFD4 A6:XFD1048576">
     <cfRule type="containsText" dxfId="40" priority="5" stopIfTrue="1" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH("Pass",A1)))</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:AE1 AP1:XFD2 A2:AB2 AD2:AE2 A3:AC5 AD4:XFD4 A6:XFD1048576">
     <cfRule type="containsText" dxfId="39" priority="6" stopIfTrue="1" operator="containsText" text="Done">
       <formula>NOT(ISERROR(SEARCH("Done",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:AE1 A2:AB2 AD2:AE2 AF4:AO4 AP1:XFD5 A3:AE5 A6:XFD1048576">
+  <conditionalFormatting sqref="A1:AE1 AP1:XFD5 A2:AB2 AD2:AE2 A3:AE5 AF4:AO4 A6:XFD1048576">
     <cfRule type="containsText" dxfId="38" priority="7" stopIfTrue="1" operator="containsText" text="na">
       <formula>NOT(ISERROR(SEARCH("na",A1)))</formula>
     </cfRule>
@@ -1965,11 +1969,11 @@
     <cfRule type="containsText" dxfId="37" priority="128" stopIfTrue="1" operator="containsText" text="Bulking">
       <formula>NOT(ISERROR(SEARCH("Bulking",C1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="129" stopIfTrue="1" operator="containsText" text="Segregating">
+    <cfRule type="containsText" dxfId="36" priority="130" operator="containsText" text="Dipping">
+      <formula>NOT(ISERROR(SEARCH("Dipping",C1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="35" priority="129" stopIfTrue="1" operator="containsText" text="Segregating">
       <formula>NOT(ISERROR(SEARCH("Segregating",C1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="35" priority="130" operator="containsText" text="Dipping">
-      <formula>NOT(ISERROR(SEARCH("Dipping",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E1048576">
@@ -1981,6 +1985,54 @@
     </cfRule>
     <cfRule type="containsText" dxfId="32" priority="127" stopIfTrue="1" operator="containsText" text="51-07">
       <formula>NOT(ISERROR(SEARCH("51-07",E1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3">
+    <cfRule type="cellIs" dxfId="31" priority="1" stopIfTrue="1" operator="greaterThan">
+      <formula>10</formula>
+    </cfRule>
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="num" val="-10"/>
+        <cfvo type="num" val="10"/>
+        <color theme="9"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{823F6022-6DA1-C340-BE78-3C97B012773D}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="3" operator="between">
+      <formula>-10</formula>
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="2" operator="between">
+      <formula>0</formula>
+      <formula>10</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="83" stopIfTrue="1" operator="greaterThan">
+      <formula>10</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="84" operator="between">
+      <formula>0</formula>
+      <formula>10</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="85" operator="between">
+      <formula>-10</formula>
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="dataBar" priority="86">
+      <dataBar>
+        <cfvo type="num" val="-10"/>
+        <cfvo type="num" val="10"/>
+        <color theme="9"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{6A5287F5-1642-5E46-9086-ECE5B7EBB9A0}</x14:id>
+        </ext>
+      </extLst>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3:I4 M3 Q4 U4 Y4">
@@ -1997,39 +2049,9 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M3 I3:I5">
-    <cfRule type="cellIs" dxfId="31" priority="155" operator="between">
-      <formula>0</formula>
+  <conditionalFormatting sqref="I3:I5 M3 M5">
+    <cfRule type="cellIs" dxfId="25" priority="113" stopIfTrue="1" operator="greaterThan">
       <formula>10</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="156" operator="between">
-      <formula>-10</formula>
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3">
-    <cfRule type="cellIs" dxfId="29" priority="83" stopIfTrue="1" operator="greaterThan">
-      <formula>10</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="84" operator="between">
-      <formula>0</formula>
-      <formula>10</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="85" operator="between">
-      <formula>-10</formula>
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="dataBar" priority="86">
-      <dataBar>
-        <cfvo type="num" val="-10"/>
-        <cfvo type="num" val="10"/>
-        <color theme="9"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6A5287F5-1642-5E46-9086-ECE5B7EBB9A0}</x14:id>
-        </ext>
-      </extLst>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5">
@@ -2046,36 +2068,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M5 M3 I3:I5">
-    <cfRule type="cellIs" dxfId="26" priority="113" stopIfTrue="1" operator="greaterThan">
-      <formula>10</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q4:Q5 U4:U5 Y4:Y5">
-    <cfRule type="cellIs" dxfId="25" priority="22" stopIfTrue="1" operator="greaterThan">
-      <formula>10</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="23" operator="between">
-      <formula>0</formula>
-      <formula>10</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="24" operator="between">
-      <formula>-10</formula>
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="cellIs" dxfId="22" priority="97" stopIfTrue="1" operator="greaterThan">
-      <formula>10</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="98" operator="between">
-      <formula>0</formula>
-      <formula>10</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="99" operator="between">
-      <formula>-10</formula>
-      <formula>0</formula>
-    </cfRule>
     <cfRule type="dataBar" priority="104">
       <dataBar>
         <cfvo type="num" val="-10"/>
@@ -2088,15 +2081,26 @@
         </ext>
       </extLst>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M5">
-    <cfRule type="cellIs" dxfId="19" priority="116" operator="between">
+    <cfRule type="cellIs" dxfId="24" priority="99" operator="between">
+      <formula>-10</formula>
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="23" priority="98" operator="between">
       <formula>0</formula>
       <formula>10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="117" operator="between">
+    <cfRule type="cellIs" dxfId="22" priority="97" stopIfTrue="1" operator="greaterThan">
+      <formula>10</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M3 I3:I5">
+    <cfRule type="cellIs" dxfId="21" priority="156" operator="between">
       <formula>-10</formula>
       <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="20" priority="155" operator="between">
+      <formula>0</formula>
+      <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M5">
@@ -2112,30 +2116,26 @@
         </ext>
       </extLst>
     </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="116" operator="between">
+      <formula>0</formula>
+      <formula>10</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="117" operator="between">
+      <formula>-10</formula>
+      <formula>0</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U3 M7 Y3 Q3:Q5">
-    <cfRule type="cellIs" dxfId="17" priority="87" stopIfTrue="1" operator="greaterThan">
-      <formula>10</formula>
-    </cfRule>
-    <cfRule type="dataBar" priority="88">
-      <dataBar>
-        <cfvo type="num" val="-10"/>
-        <cfvo type="num" val="10"/>
-        <color theme="9"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2168AD0D-F1F6-0645-A1F7-BAC20D8F0F49}</x14:id>
-        </ext>
-      </extLst>
+  <conditionalFormatting sqref="Q3:Q5 M7">
+    <cfRule type="cellIs" dxfId="17" priority="90" operator="between">
+      <formula>-10</formula>
+      <formula>0</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="16" priority="89" operator="between">
       <formula>0</formula>
       <formula>10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="90" operator="between">
-      <formula>-10</formula>
-      <formula>0</formula>
+    <cfRule type="cellIs" dxfId="15" priority="87" stopIfTrue="1" operator="greaterThan">
+      <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5">
@@ -2153,17 +2153,6 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q7">
-    <cfRule type="cellIs" dxfId="14" priority="70" stopIfTrue="1" operator="greaterThan">
-      <formula>10</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="71" operator="between">
-      <formula>0</formula>
-      <formula>10</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="72" operator="between">
-      <formula>-10</formula>
-      <formula>0</formula>
-    </cfRule>
     <cfRule type="dataBar" priority="73">
       <dataBar>
         <cfvo type="num" val="-10"/>
@@ -2175,6 +2164,44 @@
           <x14:id>{88C6B647-A323-534B-A8BE-BCED04504CD2}</x14:id>
         </ext>
       </extLst>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="70" stopIfTrue="1" operator="greaterThan">
+      <formula>10</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="71" operator="between">
+      <formula>0</formula>
+      <formula>10</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="72" operator="between">
+      <formula>-10</formula>
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U3 M7 Y3 Q3:Q5">
+    <cfRule type="dataBar" priority="88">
+      <dataBar>
+        <cfvo type="num" val="-10"/>
+        <cfvo type="num" val="10"/>
+        <color theme="9"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{2168AD0D-F1F6-0645-A1F7-BAC20D8F0F49}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U3:U5 Y3:Y5 Q4:Q5">
+    <cfRule type="cellIs" dxfId="11" priority="22" stopIfTrue="1" operator="greaterThan">
+      <formula>10</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="23" operator="between">
+      <formula>0</formula>
+      <formula>10</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="24" operator="between">
+      <formula>-10</formula>
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U5">
@@ -2192,16 +2219,8 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U7">
-    <cfRule type="cellIs" dxfId="11" priority="94" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="94" stopIfTrue="1" operator="greaterThan">
       <formula>10</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="95" operator="between">
-      <formula>0</formula>
-      <formula>10</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="96" operator="between">
-      <formula>-10</formula>
-      <formula>0</formula>
     </cfRule>
     <cfRule type="dataBar" priority="101">
       <dataBar>
@@ -2214,6 +2233,14 @@
           <x14:id>{575433CB-A8C1-9947-B91E-00435ECEFF56}</x14:id>
         </ext>
       </extLst>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="96" operator="between">
+      <formula>-10</formula>
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="95" operator="between">
+      <formula>0</formula>
+      <formula>10</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y5">
@@ -2231,17 +2258,6 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y7">
-    <cfRule type="cellIs" dxfId="8" priority="91" stopIfTrue="1" operator="greaterThan">
-      <formula>10</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="92" operator="between">
-      <formula>0</formula>
-      <formula>10</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="93" operator="between">
-      <formula>-10</formula>
-      <formula>0</formula>
-    </cfRule>
     <cfRule type="dataBar" priority="100">
       <dataBar>
         <cfvo type="num" val="-10"/>
@@ -2254,30 +2270,16 @@
         </ext>
       </extLst>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I3">
-    <cfRule type="cellIs" dxfId="5" priority="1" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="91" stopIfTrue="1" operator="greaterThan">
       <formula>10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="4" priority="92" operator="between">
       <formula>0</formula>
       <formula>10</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="3" priority="93" operator="between">
       <formula>-10</formula>
       <formula>0</formula>
-    </cfRule>
-    <cfRule type="dataBar" priority="4">
-      <dataBar>
-        <cfvo type="num" val="-10"/>
-        <cfvo type="num" val="10"/>
-        <color theme="9"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{823F6022-6DA1-C340-BE78-3C97B012773D}</x14:id>
-        </ext>
-      </extLst>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2285,6 +2287,31 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{823F6022-6DA1-C340-BE78-3C97B012773D}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0" axisPosition="none">
+              <x14:cfvo type="num">
+                <xm:f>-10</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>10</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFFC000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <x14:cfRule type="dataBar" id="{6A5287F5-1642-5E46-9086-ECE5B7EBB9A0}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0" axisPosition="none">
+              <x14:cfvo type="num">
+                <xm:f>-10</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>10</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFFC000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>I3</xm:sqref>
+        </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{C162E89A-0EB3-EF4C-96CC-1F3559432F52}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0" axisPosition="none">
@@ -2298,20 +2325,6 @@
             </x14:dataBar>
           </x14:cfRule>
           <xm:sqref>I3:I4 M3 Q4 U4 Y4</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6A5287F5-1642-5E46-9086-ECE5B7EBB9A0}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0" axisPosition="none">
-              <x14:cfvo type="num">
-                <xm:f>-10</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>10</xm:f>
-              </x14:cfvo>
-              <x14:negativeFillColor rgb="FFFFC000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>I3</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{A71541A3-C639-B243-BA15-B3310936C3CB}">
@@ -2356,20 +2369,6 @@
           <xm:sqref>M5</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2168AD0D-F1F6-0645-A1F7-BAC20D8F0F49}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0" axisPosition="none">
-              <x14:cfvo type="num">
-                <xm:f>-10</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>10</xm:f>
-              </x14:cfvo>
-              <x14:negativeFillColor rgb="FFFFC000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>U3 M7 Y3 Q3:Q5</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{1E3B95E8-412A-024F-B78A-5FF75A396677}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0" axisPosition="none">
               <x14:cfvo type="num">
@@ -2396,6 +2395,20 @@
             </x14:dataBar>
           </x14:cfRule>
           <xm:sqref>Q7</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{2168AD0D-F1F6-0645-A1F7-BAC20D8F0F49}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0" axisPosition="none">
+              <x14:cfvo type="num">
+                <xm:f>-10</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>10</xm:f>
+              </x14:cfvo>
+              <x14:negativeFillColor rgb="FFFFC000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>U3 M7 Y3 Q3:Q5</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{EA0903CE-12A8-7640-8825-984036DF080F}">
@@ -2453,20 +2466,6 @@
           </x14:cfRule>
           <xm:sqref>Y7</xm:sqref>
         </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{823F6022-6DA1-C340-BE78-3C97B012773D}">
-            <x14:dataBar minLength="0" maxLength="100" gradient="0" axisPosition="none">
-              <x14:cfvo type="num">
-                <xm:f>-10</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>10</xm:f>
-              </x14:cfvo>
-              <x14:negativeFillColor rgb="FFFFC000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>I3</xm:sqref>
-        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -2491,7 +2490,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9992943-8AF4-FD4D-A77B-14194B0A928E}">
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
@@ -2535,7 +2534,7 @@
       </c>
       <c r="B3" s="10">
         <f ca="1">TODAY()</f>
-        <v>45761</v>
+        <v>45924</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="14" t="s">
@@ -2571,7 +2570,7 @@
       <c r="D4" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="60">
+      <c r="E4" s="41">
         <v>0.7</v>
       </c>
       <c r="F4" s="1"/>
@@ -2645,29 +2644,29 @@
       <c r="L6" s="1"/>
     </row>
     <row r="7" spans="1:12" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="43">
-        <v>40</v>
-      </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
+      <c r="A7" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="8">
+        <v>50</v>
+      </c>
+      <c r="C7" s="29"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
       <c r="J7" s="1"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="B8" s="8">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C8" s="29"/>
       <c r="D8" s="1"/>
@@ -2682,10 +2681,10 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C9" s="29"/>
       <c r="D9" s="1"/>
@@ -2700,10 +2699,10 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="14" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="B10" s="8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C10" s="29"/>
       <c r="D10" s="1"/>
@@ -2718,10 +2717,10 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="8">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C11" s="29"/>
       <c r="D11" s="1"/>
@@ -2736,10 +2735,10 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="8">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C12" s="29"/>
       <c r="D12" s="1"/>
@@ -2752,12 +2751,12 @@
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="8">
-        <v>75</v>
+    <row r="13" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6">
+        <v>95</v>
       </c>
       <c r="C13" s="29"/>
       <c r="D13" s="1"/>
@@ -2770,14 +2769,10 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
     </row>
-    <row r="14" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="6">
-        <v>95</v>
-      </c>
-      <c r="C14" s="29"/>
+    <row r="14" spans="1:12" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -2788,9 +2783,7 @@
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
     </row>
-    <row r="15" spans="1:12" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -2814,20 +2807,8 @@
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
     </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="D9:L9 A9:C14 C15:L17 A2:L8">
+  <conditionalFormatting sqref="A2:L7 D8:L8 A8:C13 C14:L16">
     <cfRule type="containsText" dxfId="2" priority="1" stopIfTrue="1" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH("Pass",A2)))</formula>
     </cfRule>
@@ -2835,7 +2816,7 @@
       <formula>NOT(ISERROR(SEARCH("Done",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C15:L17 A2:L14">
+  <conditionalFormatting sqref="A2:L13 C14:L16">
     <cfRule type="containsText" dxfId="0" priority="3" stopIfTrue="1" operator="containsText" text="na">
       <formula>NOT(ISERROR(SEARCH("na",A2)))</formula>
     </cfRule>
